--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -128,7 +128,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D3"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="C2:C3">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="D2:D3">
       <formula1>ISNUMBER(D2)</formula1>
     </dataValidation>

--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -129,7 +129,7 @@
   </sheetData>
   <autoFilter ref="A1:D3"/>
   <dataValidations count="2">
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="C2:C3">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time (yyyy-MM-dd HH:mm:ss)." sqref="C2:C3">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -129,7 +129,7 @@
   </sheetData>
   <autoFilter ref="A1:D3"/>
   <dataValidations count="2">
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time (yyyy-MM-dd HH:mm:ss)." sqref="C2:C3">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" sqref="C2:C3">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -129,7 +129,7 @@
   </sheetData>
   <autoFilter ref="A1:D3"/>
   <dataValidations count="2">
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" sqref="C2:C3">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="C2:C3">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -129,7 +129,7 @@
   </sheetData>
   <autoFilter ref="A1:D3"/>
   <dataValidations count="2">
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="C2:C3">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="C2:C3">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -141,7 +141,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Email"/>
